--- a/plot_data/fig1.xlsx
+++ b/plot_data/fig1.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="plotted_data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="nodes" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="edges" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadata" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="labels" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="encodings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="metadata" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -416,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,32 +429,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>x_cm</t>
+          <t>x_layout</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>y_cm</t>
+          <t>y_layout</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>width_cm</t>
+          <t>width_layout</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>height_cm</t>
+          <t>height_layout</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>parent_node</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>stroke</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>coordinate_basis</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>label</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>display</t>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>details</t>
         </is>
       </c>
     </row>
@@ -463,28 +500,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qualified native maize dates and daily weather
-Seven BBCH endpoints; original definitions and provenance retained</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>#F4F7F8</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,29 +548,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.18</v>
+        <v>9.9</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Source labels and fitting-weather prefixes end by 2010
-Five spatial folds: 50-km blocks; 25-km cell-centre buffer
-Source-only model selection, residual teachers and normalization</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>#F4F7F8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -524,197 +596,734 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C4" t="n">
-        <v>10.35</v>
+        <v>11.6</v>
       </c>
       <c r="D4" t="n">
-        <v>18.64</v>
+        <v>18.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Six core model families
-T · nonlinear T · residual RF · residual MLP
-Thermal Transformer · source-support blend</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>#FBFCFC</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.18</v>
+        <v>0.67</v>
       </c>
       <c r="C5" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E5" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pooled benchmark
-80 sites × 8 years
-Random / coverage
-3 draws × 5 folds
-Stage errors; gross
-and net corrections</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(0.9400000000000001, 0.9400000000000001, 0.9400000000000001)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#666666</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>nonlinear_T</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.94</v>
+        <v>3.64</v>
       </c>
       <c r="C6" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E6" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Local calibration
-0/1/3/5 past years
-80-site source fit
-1 draw × 5 folds
-Five models; shared
-date-offset updates</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(0.9901960784313726, 0.9623529411764706, 0.9)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#E69F00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>transfer</t>
+          <t>residual_RF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.699999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="C7" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D7" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E7" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Climate transfer
-40 sites × 8 years
-5 zones + pooled
-3 draws × 5 folds
-Excess loss; distance
-and source support</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(0.9, 0.9619607843137256, 0.9450980392156862)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#009E73</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>residual_MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.46</v>
+        <v>9.58</v>
       </c>
       <c r="C8" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D8" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E8" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weather comparison
-40 sites × 4 years
-DWD / ERA5-Land
-3 draws × 5 folds
-Fixed-input swaps;
-own-product refits</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(0.9, 0.9447058823529412, 0.9698039215686275)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#0072B2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>thermal_transformer</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>model formulation</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(0.9337254901960784, 0.9705882352941176, 0.9913725490196079)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#56B4E9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>support_blend</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>model formulation</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(0.9533333333333334, 0.9133333333333333, 0.9333333333333333)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#882255</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>#EEF3F7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(a)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Model performance</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>80 sites × 8 years · 3 draws
+Random / coverage sampling
+Stage errors; benefit and harm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>#EFF5F1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Local information</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0, 1, 3 or 5 past local years
+80-site coverage fit · 1 draw
+Five models; shared date offsets</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>#F8F3E9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Environmental transfer</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>40 sites × 8 years · 3 draws
+5 temperature zones + pooled
+Paired transfer loss and distance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>#F3EFF7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>(d)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Weather inputs</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>40 sites × 4 years · 3 draws
+DWD station / ERA5-Land inputs
+Weather swaps and refitting</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Later held outcomes: 2011–2025; weather cohort: 2011–2024
-Identical native targets within each paired experiment
-Head-balanced penalised MAE; invalid dates receive 366 d
-Conditional 95% intervals from paired spatial/station-block resampling</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+      <c r="B15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>#EAF1F4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#9EAFBA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>shared_inputs</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>connector junction</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>conceptual connection</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>connector junction</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>conceptual connection</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -727,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -738,32 +1347,67 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>x_cm</t>
+          <t>x_layout</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>y_cm</t>
+          <t>y_layout</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>width_cm</t>
+          <t>width_layout</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>height_cm</t>
+          <t>height_layout</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>kind</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>parent_node</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>fill</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>stroke</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>coordinate_basis</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>panel</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>label</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>display</t>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>details</t>
         </is>
       </c>
     </row>
@@ -774,28 +1418,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="D2" t="n">
-        <v>18.64</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>1.5</v>
+        <v>2.85</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qualified native maize dates and daily weather
-Seven BBCH endpoints; original definitions and provenance retained</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>#F4F7F8</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -804,29 +1466,46 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.18</v>
+        <v>9.9</v>
       </c>
       <c r="C3" t="n">
-        <v>12.9</v>
+        <v>14.4</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.95</v>
+        <v>2.85</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Source labels and fitting-weather prefixes end by 2010
-Five spatial folds: 50-km blocks; 25-km cell-centre buffer
-Source-only model selection, residual teachers and normalization</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>#F4F7F8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -835,197 +1514,734 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="C4" t="n">
-        <v>10.35</v>
+        <v>11.6</v>
       </c>
       <c r="D4" t="n">
-        <v>18.64</v>
+        <v>18.2</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Six core model families
-T · nonlinear T · residual RF · residual MLP
-Thermal Transformer · source-support blend</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>#FBFCFC</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.18</v>
+        <v>0.67</v>
       </c>
       <c r="C5" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D5" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E5" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pooled benchmark
-80 sites × 8 years
-Random / coverage
-3 draws × 5 folds
-Stage errors; gross
-and net corrections</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(0.9400000000000001, 0.9400000000000001, 0.9400000000000001)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>#666666</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>nonlinear_T</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.94</v>
+        <v>3.64</v>
       </c>
       <c r="C6" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D6" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E6" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Local calibration
-0/1/3/5 past years
-80-site source fit
-1 draw × 5 folds
-Five models; shared
-date-offset updates</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(0.9901960784313726, 0.9623529411764706, 0.9)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>#E69F00</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>transfer</t>
+          <t>residual_RF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9.699999999999999</v>
+        <v>6.61</v>
       </c>
       <c r="C7" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D7" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E7" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Climate transfer
-40 sites × 8 years
-5 zones + pooled
-3 draws × 5 folds
-Excess loss; distance
-and source support</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(0.9, 0.9619607843137256, 0.9450980392156862)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>#009E73</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>residual_MLP</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14.46</v>
+        <v>9.58</v>
       </c>
       <c r="C8" t="n">
-        <v>4.85</v>
+        <v>11.75</v>
       </c>
       <c r="D8" t="n">
-        <v>4.36</v>
+        <v>2.78</v>
       </c>
       <c r="E8" t="n">
-        <v>4.55</v>
+        <v>1.24</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Weather comparison
-40 sites × 4 years
-DWD / ERA5-Land
-3 draws × 5 folds
-Fixed-input swaps;
-own-product refits</t>
+          <t>model formulation</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(0.9, 0.9447058823529412, 0.9698039215686275)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>#0072B2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>thermal_transformer</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="C9" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>model formulation</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(0.9337254901960784, 0.9705882352941176, 0.9913725490196079)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>#56B4E9</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>support_blend</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>15.52</v>
+      </c>
+      <c r="C10" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>model formulation</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(0.9533333333333334, 0.9133333333333333, 0.9333333333333333)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>#882255</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>#EEF3F7</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(a)</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Model performance</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>80 sites × 8 years · 3 draws
+Random / coverage sampling
+Stage errors; benefit and harm</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>#EFF5F1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Local information</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0, 1, 3 or 5 past local years
+80-site coverage fit · 1 draw
+Five models; shared date offsets</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>#F8F3E9</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Environmental transfer</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>40 sites × 8 years · 3 draws
+5 temperature zones + pooled
+Paired transfer loss and distance</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D14" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>parallel comparison</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>#F3EFF7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>#B8C5CD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>(d)</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Weather inputs</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>40 sites × 4 years · 3 draws
+DWD station / ERA5-Land inputs
+Weather swaps and refitting</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="D9" t="n">
-        <v>18.64</v>
-      </c>
-      <c r="E9" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Later held outcomes: 2011–2025; weather cohort: 2011–2024
-Identical native targets within each paired experiment
-Head-balanced penalised MAE; invalid dates receive 366 d
-Conditional 95% intervals from paired spatial/station-block resampling</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>conceptual workflow; no measured result</t>
-        </is>
-      </c>
+      <c r="B15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shared</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>#EAF1F4</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>#9EAFBA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>conceptual study design; no measured performance values</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>shared_inputs</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>connector junction</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>conceptual connection</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>connector junction</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>arbitrary diagram layout coordinates; not measured or geographic</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>conceptual connection</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1038,7 +2254,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1054,27 +2270,12 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>start_x_cm</t>
+          <t>path</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>start_y_cm</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>end_x_cm</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>end_y_cm</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>via</t>
+          <t>direction</t>
         </is>
       </c>
     </row>
@@ -1086,22 +2287,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>separation</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D2" t="n">
-        <v>15.52</v>
-      </c>
-      <c r="E2" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F2" t="n">
-        <v>14.93</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+          <t>shared_inputs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>[[4.75, 14.4], [4.75, 14.1], [9.5, 14.1]]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1111,49 +2309,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>models</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="D3" t="n">
-        <v>12.82</v>
-      </c>
-      <c r="E3" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+          <t>shared_inputs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[[14.25, 14.4], [14.25, 14.1], [9.5, 14.1]]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>shared_inputs</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>models</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>benchmark</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="F4" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>shared branch connector at y=9.85 cm</t>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[[9.5, 14.1], [9.5, 13.9]]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>source to target</t>
         </is>
       </c>
     </row>
@@ -1165,53 +2353,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>7.119999999999999</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7.119999999999999</v>
-      </c>
-      <c r="F5" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>shared branch connector at y=9.85 cm</t>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[[9.5, 11.6], [9.5, 11.1], [4.75, 11.1], [4.75, 10.73]]</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>source to target</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>benchmark</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>transfer</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="D6" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E6" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="F6" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>shared branch connector at y=9.85 cm</t>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[[9.1, 9.1], [9.5, 9.1], [9.5, 3.55]]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>source to target</t>
         </is>
       </c>
     </row>
@@ -1223,76 +2397,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>weather</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="D7" t="n">
-        <v>9.85</v>
-      </c>
-      <c r="E7" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="F7" t="n">
-        <v>9.48</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>shared branch connector at y=9.85 cm</t>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[[9.5, 11.6], [9.5, 11.1], [14.25, 11.1], [14.25, 10.73]]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>source to target</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>local</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[[9.9, 9.1], [9.5, 9.1], [9.5, 3.55]]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>models</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>7.119999999999999</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E9" t="n">
-        <v>7.119999999999999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[[9.5, 11.6], [9.5, 11.1], [0.12, 11.1], [0.12, 7.15], [4.75, 7.15], [4.75, 6.880000000000001]]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1302,47 +2463,85 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="D10" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E10" t="n">
-        <v>11.88</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[[9.1, 5.25], [9.5, 5.25], [9.5, 3.55]]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>weather</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[[9.5, 11.6], [9.5, 11.1], [18.88, 11.1], [18.88, 7.15], [14.25, 7.15], [14.25, 6.880000000000001]]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[[9.9, 5.25], [9.5, 5.25], [9.5, 3.55]]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>paired_comparisons</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="C11" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E11" t="n">
-        <v>16.64</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[[9.5, 3.55], [9.5, 3.08]]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>source to target</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1355,6 +2554,1195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>label</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>font_pt</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>font_weight</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>horizontal_alignment</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>container_node</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>within_container</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>x_layout</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>y_layout</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>question</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>How do model structure and input information
+jointly influence phenology transferability?</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>12</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="b">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>18.25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>data_heading</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Data and provenance</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>qualified_data</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>16.73</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>data_body</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Observed maize event dates
+Daily weather at native cells
+Seven BBCH endpoints</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>qualified_data</t>
+        </is>
+      </c>
+      <c r="G4" t="b">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>control_heading</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Calibration and testing</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>separation</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>16.73</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>control_body</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fitting data end by 2010
+5 folds · 50-km spatial blocks
+25-km cell-centre buffer</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>separation</t>
+        </is>
+      </c>
+      <c r="G6" t="b">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>models_heading</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Six model formulations</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>models</t>
+        </is>
+      </c>
+      <c r="G7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I7" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>model_T</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>12</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="G8" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I8" t="n">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>model_nonlinear_T</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Nonlinear
+T</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>12</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>nonlinear_T</t>
+        </is>
+      </c>
+      <c r="G9" t="b">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="I9" t="n">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>model_residual_RF</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Residual
+RF</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>12</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>residual_RF</t>
+        </is>
+      </c>
+      <c r="G10" t="b">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>model_residual_MLP</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Residual
+MLP</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>residual_MLP</t>
+        </is>
+      </c>
+      <c r="G11" t="b">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>model_thermal_transformer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Thermal
+Transformer</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>thermal_transformer</t>
+        </is>
+      </c>
+      <c r="G12" t="b">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>13.94</v>
+      </c>
+      <c r="I12" t="n">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>model_support_blend</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Support
+blend</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>12</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>center</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>support_blend</t>
+        </is>
+      </c>
+      <c r="G13" t="b">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12.37</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>benchmark_panel</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>(a)</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>benchmark_heading</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Model performance</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I15" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>benchmark_body</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>80 sites × 8 years · 3 draws
+Random / coverage sampling
+Stage errors; benefit and harm</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="G16" t="b">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>local_panel</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>local_heading</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Local information</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="I18" t="n">
+        <v>10.12</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>local_body</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0, 1, 3 or 5 past local years
+80-site coverage fit · 1 draw
+Five models; shared date offsets</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="G19" t="b">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>transfer_panel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>transfer_heading</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Environmental transfer</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I21" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>transfer_body</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>40 sites × 8 years · 3 draws
+5 temperature zones + pooled
+Paired transfer loss and distance</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>weather_panel</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>(d)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>weather_heading</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Weather inputs</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="I24" t="n">
+        <v>6.27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>weather_body</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>40 sites × 4 years · 3 draws
+DWD station / ERA5-Land inputs
+Weather swaps and refitting</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>evaluation_heading</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Paired evaluation under specified conditions</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>12</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>bold</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I26" t="n">
+        <v>2.53</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>evaluation_body</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2011–2025 outcomes; weather cohort: 2011–2024
+Penalised MAE; equal endpoint weights · Invalid dates: 366 d
+95% conditional intervals · Spatial / station groups</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>evaluation</t>
+        </is>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#666666</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>nonlinear_T</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>#E69F00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>residual_RF</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>#009E73</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>residual_MLP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>#0072B2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>thermal_transformer</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>#56B4E9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>support_blend</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>#882255</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>

--- a/plot_data/fig1.xlsx
+++ b/plot_data/fig1.xlsx
@@ -2554,7 +2554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2607,13 +2607,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>data_heading</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>How do model structure and input information
-jointly influence phenology transferability?</t>
+          <t>Data and provenance</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2626,78 +2625,82 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>center</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>qualified_data</t>
+        </is>
+      </c>
       <c r="G2" t="b">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>9.5</v>
+        <v>0.8</v>
       </c>
       <c r="I2" t="n">
-        <v>18.25</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>data_heading</t>
+          <t>data_body</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
-        <is>
-          <t>Data and provenance</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>qualified_data</t>
-        </is>
-      </c>
-      <c r="G3" t="b">
-        <v>1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>16.73</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>data_body</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
         <is>
           <t>Observed maize event dates
 Daily weather at native cells
 Seven BBCH endpoints</t>
         </is>
       </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>qualified_data</t>
+        </is>
+      </c>
+      <c r="G3" t="b">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>control_heading</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Calibration and testing</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2707,77 +2710,77 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>qualified_data</t>
+          <t>separation</t>
         </is>
       </c>
       <c r="G4" t="b">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8</v>
+        <v>10.3</v>
       </c>
       <c r="I4" t="n">
-        <v>15.55</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>control_heading</t>
+          <t>control_body</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
-        <is>
-          <t>Calibration and testing</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>separation</t>
-        </is>
-      </c>
-      <c r="G5" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>16.73</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>control_body</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
         <is>
           <t>Fitting data end by 2010
 5 folds · 50-km spatial blocks
 25-km cell-centre buffer</t>
         </is>
       </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>separation</t>
+        </is>
+      </c>
+      <c r="G5" t="b">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I5" t="n">
+        <v>15.55</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>models_heading</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Six model formulations</t>
+        </is>
+      </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2787,28 +2790,28 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>separation</t>
+          <t>models</t>
         </is>
       </c>
       <c r="G6" t="b">
         <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>10.3</v>
+        <v>0.8</v>
       </c>
       <c r="I6" t="n">
-        <v>15.55</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>models_heading</t>
+          <t>model_T</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Six model formulations</t>
+          <t>T</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -2816,38 +2819,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bold</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>center</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>models</t>
+          <t>T</t>
         </is>
       </c>
       <c r="G7" t="b">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8</v>
+        <v>2.06</v>
       </c>
       <c r="I7" t="n">
-        <v>13.5</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>model_T</t>
+          <t>model_nonlinear_T</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>Nonlinear
+T</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -2865,14 +2869,14 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>nonlinear_T</t>
         </is>
       </c>
       <c r="G8" t="b">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2.06</v>
+        <v>5.03</v>
       </c>
       <c r="I8" t="n">
         <v>12.37</v>
@@ -2881,13 +2885,13 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>model_nonlinear_T</t>
+          <t>model_residual_RF</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Nonlinear
-T</t>
+          <t>Residual
+RF</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -2905,14 +2909,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>nonlinear_T</t>
+          <t>residual_RF</t>
         </is>
       </c>
       <c r="G9" t="b">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>5.03</v>
+        <v>8</v>
       </c>
       <c r="I9" t="n">
         <v>12.37</v>
@@ -2921,13 +2925,13 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>model_residual_RF</t>
+          <t>model_residual_MLP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Residual
-RF</t>
+MLP</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -2945,14 +2949,14 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>residual_RF</t>
+          <t>residual_MLP</t>
         </is>
       </c>
       <c r="G10" t="b">
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>10.97</v>
       </c>
       <c r="I10" t="n">
         <v>12.37</v>
@@ -2961,13 +2965,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>model_residual_MLP</t>
+          <t>model_thermal_transformer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Residual
-MLP</t>
+          <t>Thermal
+Transformer</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -2985,14 +2989,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>residual_MLP</t>
+          <t>thermal_transformer</t>
         </is>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>10.97</v>
+        <v>13.94</v>
       </c>
       <c r="I11" t="n">
         <v>12.37</v>
@@ -3001,13 +3005,13 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>model_thermal_transformer</t>
+          <t>model_support_blend</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Thermal
-Transformer</t>
+          <t>Support
+blend</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -3025,14 +3029,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>thermal_transformer</t>
+          <t>support_blend</t>
         </is>
       </c>
       <c r="G12" t="b">
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>13.94</v>
+        <v>16.91</v>
       </c>
       <c r="I12" t="n">
         <v>12.37</v>
@@ -3041,13 +3045,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>model_support_blend</t>
+          <t>benchmark_panel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Support
-blend</t>
+          <t>(a)</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -3055,38 +3058,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>left</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>support_blend</t>
+          <t>benchmark</t>
         </is>
       </c>
       <c r="G13" t="b">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>16.91</v>
+        <v>0.8</v>
       </c>
       <c r="I13" t="n">
-        <v>12.37</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>benchmark_panel</t>
+          <t>benchmark_heading</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>(a)</t>
+          <t>Model performance</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -3111,7 +3114,7 @@
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8</v>
+        <v>1.55</v>
       </c>
       <c r="I14" t="n">
         <v>10.12</v>
@@ -3120,61 +3123,61 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>benchmark_heading</t>
+          <t>benchmark_body</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
-        <is>
-          <t>Model performance</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>benchmark</t>
-        </is>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I15" t="n">
-        <v>10.12</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>benchmark_body</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
         <is>
           <t>80 sites × 8 years · 3 draws
 Random / coverage sampling
 Stage errors; benefit and harm</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>local_panel</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>(b)</t>
+        </is>
+      </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3184,28 +3187,28 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>benchmark</t>
+          <t>local</t>
         </is>
       </c>
       <c r="G16" t="b">
         <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8</v>
+        <v>10.3</v>
       </c>
       <c r="I16" t="n">
-        <v>8.869999999999999</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>local_panel</t>
+          <t>local_heading</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>(b)</t>
+          <t>Local information</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -3230,7 +3233,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>10.3</v>
+        <v>11.05</v>
       </c>
       <c r="I17" t="n">
         <v>10.12</v>
@@ -3239,61 +3242,61 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>local_heading</t>
+          <t>local_body</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
-        <is>
-          <t>Local information</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>local</t>
-        </is>
-      </c>
-      <c r="G18" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="I18" t="n">
-        <v>10.12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>local_body</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
         <is>
           <t>0, 1, 3 or 5 past local years
 80-site coverage fit · 1 draw
 Five models; shared date offsets</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>12</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>local</t>
+        </is>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8.869999999999999</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>transfer_panel</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>(c)</t>
+        </is>
+      </c>
       <c r="C19" t="n">
         <v>12</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3303,28 +3306,28 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>transfer</t>
         </is>
       </c>
       <c r="G19" t="b">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>10.3</v>
+        <v>0.8</v>
       </c>
       <c r="I19" t="n">
-        <v>8.869999999999999</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>transfer_panel</t>
+          <t>transfer_heading</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>(c)</t>
+          <t>Environmental transfer</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -3349,7 +3352,7 @@
         <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8</v>
+        <v>1.55</v>
       </c>
       <c r="I20" t="n">
         <v>6.27</v>
@@ -3358,61 +3361,61 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>transfer_heading</t>
+          <t>transfer_body</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
-        <is>
-          <t>Environmental transfer</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>12</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>transfer</t>
-        </is>
-      </c>
-      <c r="G21" t="b">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="I21" t="n">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>transfer_body</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
         <is>
           <t>40 sites × 8 years · 3 draws
 5 temperature zones + pooled
 Paired transfer loss and distance</t>
         </is>
       </c>
+      <c r="C21" t="n">
+        <v>12</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>transfer</t>
+        </is>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I21" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>weather_panel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>(d)</t>
+        </is>
+      </c>
       <c r="C22" t="n">
         <v>12</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3422,28 +3425,28 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>transfer</t>
+          <t>weather</t>
         </is>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8</v>
+        <v>10.3</v>
       </c>
       <c r="I22" t="n">
-        <v>5.02</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>weather_panel</t>
+          <t>weather_heading</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>(d)</t>
+          <t>Weather inputs</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -3468,7 +3471,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="n">
-        <v>10.3</v>
+        <v>11.05</v>
       </c>
       <c r="I23" t="n">
         <v>6.27</v>
@@ -3477,61 +3480,61 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>weather_heading</t>
+          <t>weather_body</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
-        <is>
-          <t>Weather inputs</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>12</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>weather</t>
-        </is>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="I24" t="n">
-        <v>6.27</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>weather_body</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
         <is>
           <t>40 sites × 4 years · 3 draws
 DWD station / ERA5-Land inputs
 Weather swaps and refitting</t>
         </is>
       </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>left</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>weather</t>
+        </is>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5.02</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>evaluation_heading</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Paired evaluation under specified conditions</t>
+        </is>
+      </c>
       <c r="C25" t="n">
         <v>12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3541,96 +3544,57 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>weather</t>
+          <t>evaluation</t>
         </is>
       </c>
       <c r="G25" t="b">
         <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>10.3</v>
+        <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>5.02</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>evaluation_heading</t>
+          <t>evaluation_body</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
-        <is>
-          <t>Paired evaluation under specified conditions</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>bold</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>left</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>evaluation</t>
-        </is>
-      </c>
-      <c r="G26" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="I26" t="n">
-        <v>2.53</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>evaluation_body</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
         <is>
           <t>2011–2025 outcomes; weather cohort: 2011–2024
 Penalised MAE; equal endpoint weights · Invalid dates: 366 d
 95% conditional intervals · Spatial / station groups</t>
         </is>
       </c>
-      <c r="C27" t="n">
+      <c r="C26" t="n">
         <v>12</v>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>normal</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>left</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>evaluation</t>
         </is>
       </c>
-      <c r="G27" t="b">
+      <c r="G26" t="b">
         <v>1</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H26" t="n">
         <v>0.8</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I26" t="n">
         <v>1.4</v>
       </c>
     </row>
